--- a/reference/print_1st2ndtrip.xlsx
+++ b/reference/print_1st2ndtrip.xlsx
@@ -8,12 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Marlou\Desktop\MY PROJECT\reference\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC95FD67-D67F-4C72-925C-57EEA5256B6C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{819712EA-E08A-4081-9FF9-065F079E6006}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -677,59 +678,59 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
+    <xf numFmtId="3" fontId="2" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="3" fontId="2" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
+    <xf numFmtId="1" fontId="5" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="5" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
-    <xf numFmtId="1" fontId="5" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
-    <xf numFmtId="3" fontId="2" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyAlignment="1">
@@ -1060,23 +1061,23 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:16" ht="36.75" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A1" s="65" t="s">
+      <c r="A1" s="52" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="66"/>
-      <c r="C1" s="66"/>
-      <c r="D1" s="66"/>
-      <c r="E1" s="66"/>
-      <c r="F1" s="66"/>
-      <c r="G1" s="66"/>
-      <c r="H1" s="66"/>
-      <c r="I1" s="66"/>
-      <c r="J1" s="66"/>
-      <c r="K1" s="66"/>
-      <c r="L1" s="66"/>
-      <c r="M1" s="66"/>
-      <c r="N1" s="66"/>
-      <c r="O1" s="67"/>
+      <c r="B1" s="53"/>
+      <c r="C1" s="53"/>
+      <c r="D1" s="53"/>
+      <c r="E1" s="53"/>
+      <c r="F1" s="53"/>
+      <c r="G1" s="53"/>
+      <c r="H1" s="53"/>
+      <c r="I1" s="53"/>
+      <c r="J1" s="53"/>
+      <c r="K1" s="53"/>
+      <c r="L1" s="53"/>
+      <c r="M1" s="53"/>
+      <c r="N1" s="53"/>
+      <c r="O1" s="54"/>
       <c r="P1" t="s">
         <v>1</v>
       </c>
@@ -1086,37 +1087,37 @@
       <c r="B2" s="77" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="57"/>
-      <c r="E2" s="76" t="s">
+      <c r="C2" s="61"/>
+      <c r="E2" s="58" t="s">
         <v>3</v>
       </c>
-      <c r="F2" s="55"/>
-      <c r="G2" s="59"/>
-      <c r="H2" s="55"/>
-      <c r="I2" s="55"/>
-      <c r="J2" s="57"/>
-      <c r="K2" s="55"/>
+      <c r="F2" s="59"/>
+      <c r="G2" s="60"/>
+      <c r="H2" s="59"/>
+      <c r="I2" s="59"/>
+      <c r="J2" s="61"/>
+      <c r="K2" s="59"/>
       <c r="L2" s="68"/>
-      <c r="M2" s="58" t="s">
+      <c r="M2" s="72" t="s">
         <v>4</v>
       </c>
-      <c r="N2" s="63" t="s">
+      <c r="N2" s="66" t="s">
         <v>5</v>
       </c>
       <c r="O2" s="4"/>
     </row>
     <row r="3" spans="1:16" ht="28.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A3" s="1"/>
-      <c r="B3" s="55"/>
-      <c r="C3" s="57"/>
-      <c r="G3" s="60" t="s">
+      <c r="B3" s="59"/>
+      <c r="C3" s="61"/>
+      <c r="G3" s="73" t="s">
         <v>6</v>
       </c>
-      <c r="H3" s="55"/>
-      <c r="I3" s="55"/>
-      <c r="L3" s="55"/>
-      <c r="M3" s="59"/>
-      <c r="N3" s="64"/>
+      <c r="H3" s="59"/>
+      <c r="I3" s="59"/>
+      <c r="L3" s="59"/>
+      <c r="M3" s="60"/>
+      <c r="N3" s="66"/>
       <c r="O3" s="4"/>
     </row>
     <row r="4" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -1124,10 +1125,10 @@
       <c r="L4" t="s">
         <v>7</v>
       </c>
-      <c r="M4" s="71" t="s">
+      <c r="M4" s="62" t="s">
         <v>8</v>
       </c>
-      <c r="N4" s="53"/>
+      <c r="N4" s="63"/>
       <c r="O4" s="8"/>
     </row>
     <row r="5" spans="1:16" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -1135,14 +1136,14 @@
       <c r="B5" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="C5" s="52" t="s">
+      <c r="C5" s="65" t="s">
         <v>10</v>
       </c>
-      <c r="D5" s="53"/>
-      <c r="E5" s="54" t="s">
+      <c r="D5" s="63"/>
+      <c r="E5" s="74" t="s">
         <v>11</v>
       </c>
-      <c r="F5" s="55"/>
+      <c r="F5" s="59"/>
       <c r="G5" s="13" t="s">
         <v>12</v>
       </c>
@@ -1156,8 +1157,8 @@
       <c r="L5" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="M5" s="61"/>
-      <c r="N5" s="62"/>
+      <c r="M5" s="76"/>
+      <c r="N5" s="56"/>
       <c r="O5" s="8"/>
     </row>
     <row r="6" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -1165,19 +1166,19 @@
       <c r="B6" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="C6" s="52"/>
-      <c r="D6" s="53"/>
-      <c r="E6" s="53"/>
-      <c r="F6" s="53"/>
-      <c r="G6" s="53"/>
+      <c r="C6" s="65"/>
+      <c r="D6" s="63"/>
+      <c r="E6" s="63"/>
+      <c r="F6" s="63"/>
+      <c r="G6" s="63"/>
       <c r="I6" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="J6" s="52"/>
-      <c r="K6" s="53"/>
-      <c r="L6" s="53"/>
-      <c r="M6" s="53"/>
-      <c r="N6" s="53"/>
+      <c r="J6" s="65"/>
+      <c r="K6" s="63"/>
+      <c r="L6" s="63"/>
+      <c r="M6" s="63"/>
+      <c r="N6" s="63"/>
       <c r="O6" s="8"/>
     </row>
     <row r="7" spans="1:16" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -1185,18 +1186,18 @@
       <c r="B7" t="s">
         <v>18</v>
       </c>
-      <c r="D7" s="69"/>
-      <c r="E7" s="62"/>
-      <c r="F7" s="62"/>
-      <c r="G7" s="62"/>
+      <c r="D7" s="55"/>
+      <c r="E7" s="56"/>
+      <c r="F7" s="56"/>
+      <c r="G7" s="56"/>
       <c r="I7" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="J7" s="75"/>
-      <c r="K7" s="62"/>
-      <c r="L7" s="62"/>
-      <c r="M7" s="62"/>
-      <c r="N7" s="62"/>
+      <c r="J7" s="57"/>
+      <c r="K7" s="56"/>
+      <c r="L7" s="56"/>
+      <c r="M7" s="56"/>
+      <c r="N7" s="56"/>
       <c r="O7" s="8"/>
     </row>
     <row r="8" spans="1:16" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -1217,19 +1218,19 @@
       <c r="B9" t="s">
         <v>21</v>
       </c>
-      <c r="C9" s="52"/>
-      <c r="D9" s="53"/>
-      <c r="E9" s="53"/>
-      <c r="F9" s="53"/>
-      <c r="G9" s="53"/>
+      <c r="C9" s="65"/>
+      <c r="D9" s="63"/>
+      <c r="E9" s="63"/>
+      <c r="F9" s="63"/>
+      <c r="G9" s="63"/>
       <c r="I9" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="J9" s="52"/>
-      <c r="K9" s="53"/>
-      <c r="L9" s="53"/>
-      <c r="M9" s="53"/>
-      <c r="N9" s="53"/>
+      <c r="J9" s="65"/>
+      <c r="K9" s="63"/>
+      <c r="L9" s="63"/>
+      <c r="M9" s="63"/>
+      <c r="N9" s="63"/>
       <c r="O9" s="8"/>
     </row>
     <row r="10" spans="1:16" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -1256,11 +1257,11 @@
       <c r="J11" s="17" t="s">
         <v>26</v>
       </c>
-      <c r="L11" s="72" t="s">
+      <c r="L11" s="69" t="s">
         <v>27</v>
       </c>
-      <c r="M11" s="73"/>
-      <c r="N11" s="74"/>
+      <c r="M11" s="70"/>
+      <c r="N11" s="71"/>
       <c r="O11" s="8"/>
     </row>
     <row r="12" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -1397,12 +1398,12 @@
       <c r="F24" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="G24" s="70" t="str">
+      <c r="G24" s="64" t="str">
         <f>M4</f>
         <v>11-15-2025</v>
       </c>
-      <c r="H24" s="53"/>
-      <c r="I24" s="53"/>
+      <c r="H24" s="63"/>
+      <c r="I24" s="63"/>
       <c r="K24" s="45" t="s">
         <v>37</v>
       </c>
@@ -1430,63 +1431,63 @@
     </row>
     <row r="26" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="27" spans="1:16" ht="37.799999999999997" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A27" s="65" t="s">
+      <c r="A27" s="52" t="s">
         <v>0</v>
       </c>
-      <c r="B27" s="66"/>
-      <c r="C27" s="66"/>
-      <c r="D27" s="66"/>
-      <c r="E27" s="66"/>
-      <c r="F27" s="66"/>
-      <c r="G27" s="66"/>
-      <c r="H27" s="66"/>
-      <c r="I27" s="66"/>
-      <c r="J27" s="66"/>
-      <c r="K27" s="66"/>
-      <c r="L27" s="66"/>
-      <c r="M27" s="66"/>
-      <c r="N27" s="66"/>
-      <c r="O27" s="67"/>
+      <c r="B27" s="53"/>
+      <c r="C27" s="53"/>
+      <c r="D27" s="53"/>
+      <c r="E27" s="53"/>
+      <c r="F27" s="53"/>
+      <c r="G27" s="53"/>
+      <c r="H27" s="53"/>
+      <c r="I27" s="53"/>
+      <c r="J27" s="53"/>
+      <c r="K27" s="53"/>
+      <c r="L27" s="53"/>
+      <c r="M27" s="53"/>
+      <c r="N27" s="53"/>
+      <c r="O27" s="54"/>
       <c r="P27" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="28" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A28" s="1"/>
-      <c r="B28" s="56" t="s">
+      <c r="B28" s="75" t="s">
         <v>2</v>
       </c>
-      <c r="C28" s="57"/>
-      <c r="E28" s="76" t="s">
+      <c r="C28" s="61"/>
+      <c r="E28" s="58" t="s">
         <v>3</v>
       </c>
-      <c r="F28" s="55"/>
-      <c r="G28" s="59"/>
-      <c r="H28" s="55"/>
-      <c r="I28" s="55"/>
-      <c r="J28" s="57"/>
-      <c r="K28" s="55"/>
+      <c r="F28" s="59"/>
+      <c r="G28" s="60"/>
+      <c r="H28" s="59"/>
+      <c r="I28" s="59"/>
+      <c r="J28" s="61"/>
+      <c r="K28" s="59"/>
       <c r="L28" s="68"/>
-      <c r="M28" s="58" t="s">
+      <c r="M28" s="72" t="s">
         <v>4</v>
       </c>
-      <c r="N28" s="63" t="s">
+      <c r="N28" s="66" t="s">
         <v>39</v>
       </c>
       <c r="O28" s="4"/>
     </row>
     <row r="29" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A29" s="1"/>
-      <c r="B29" s="55"/>
-      <c r="C29" s="57"/>
-      <c r="G29" s="60" t="s">
+      <c r="B29" s="59"/>
+      <c r="C29" s="61"/>
+      <c r="G29" s="73" t="s">
         <v>6</v>
       </c>
-      <c r="H29" s="55"/>
-      <c r="I29" s="55"/>
-      <c r="L29" s="55"/>
-      <c r="M29" s="59"/>
-      <c r="N29" s="64"/>
+      <c r="H29" s="59"/>
+      <c r="I29" s="59"/>
+      <c r="L29" s="59"/>
+      <c r="M29" s="60"/>
+      <c r="N29" s="67"/>
       <c r="O29" s="4"/>
     </row>
     <row r="30" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -1494,10 +1495,10 @@
       <c r="L30" t="s">
         <v>7</v>
       </c>
-      <c r="M30" s="71" t="s">
+      <c r="M30" s="62" t="s">
         <v>40</v>
       </c>
-      <c r="N30" s="53"/>
+      <c r="N30" s="63"/>
       <c r="O30" s="8"/>
     </row>
     <row r="31" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -1505,14 +1506,14 @@
       <c r="B31" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="C31" s="52" t="s">
+      <c r="C31" s="65" t="s">
         <v>10</v>
       </c>
-      <c r="D31" s="53"/>
-      <c r="E31" s="54" t="s">
+      <c r="D31" s="63"/>
+      <c r="E31" s="74" t="s">
         <v>11</v>
       </c>
-      <c r="F31" s="55"/>
+      <c r="F31" s="59"/>
       <c r="G31" s="13" t="s">
         <v>12</v>
       </c>
@@ -1526,10 +1527,10 @@
       <c r="L31" t="s">
         <v>15</v>
       </c>
-      <c r="M31" s="70" t="s">
+      <c r="M31" s="64" t="s">
         <v>41</v>
       </c>
-      <c r="N31" s="53"/>
+      <c r="N31" s="63"/>
       <c r="O31" s="8"/>
     </row>
     <row r="32" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -1537,19 +1538,19 @@
       <c r="B32" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="C32" s="52"/>
-      <c r="D32" s="53"/>
-      <c r="E32" s="53"/>
-      <c r="F32" s="53"/>
-      <c r="G32" s="53"/>
+      <c r="C32" s="65"/>
+      <c r="D32" s="63"/>
+      <c r="E32" s="63"/>
+      <c r="F32" s="63"/>
+      <c r="G32" s="63"/>
       <c r="I32" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="J32" s="52"/>
-      <c r="K32" s="53"/>
-      <c r="L32" s="53"/>
-      <c r="M32" s="53"/>
-      <c r="N32" s="53"/>
+      <c r="J32" s="65"/>
+      <c r="K32" s="63"/>
+      <c r="L32" s="63"/>
+      <c r="M32" s="63"/>
+      <c r="N32" s="63"/>
       <c r="O32" s="8"/>
     </row>
     <row r="33" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -1557,18 +1558,18 @@
       <c r="B33" t="s">
         <v>18</v>
       </c>
-      <c r="D33" s="69"/>
-      <c r="E33" s="62"/>
-      <c r="F33" s="62"/>
-      <c r="G33" s="62"/>
+      <c r="D33" s="55"/>
+      <c r="E33" s="56"/>
+      <c r="F33" s="56"/>
+      <c r="G33" s="56"/>
       <c r="I33" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="J33" s="75"/>
-      <c r="K33" s="62"/>
-      <c r="L33" s="62"/>
-      <c r="M33" s="62"/>
-      <c r="N33" s="62"/>
+      <c r="J33" s="57"/>
+      <c r="K33" s="56"/>
+      <c r="L33" s="56"/>
+      <c r="M33" s="56"/>
+      <c r="N33" s="56"/>
       <c r="O33" s="8"/>
     </row>
     <row r="34" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -1589,19 +1590,19 @@
       <c r="B35" t="s">
         <v>21</v>
       </c>
-      <c r="C35" s="52"/>
-      <c r="D35" s="53"/>
-      <c r="E35" s="53"/>
-      <c r="F35" s="53"/>
-      <c r="G35" s="53"/>
+      <c r="C35" s="65"/>
+      <c r="D35" s="63"/>
+      <c r="E35" s="63"/>
+      <c r="F35" s="63"/>
+      <c r="G35" s="63"/>
       <c r="I35" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="J35" s="52"/>
-      <c r="K35" s="53"/>
-      <c r="L35" s="53"/>
-      <c r="M35" s="53"/>
-      <c r="N35" s="53"/>
+      <c r="J35" s="65"/>
+      <c r="K35" s="63"/>
+      <c r="L35" s="63"/>
+      <c r="M35" s="63"/>
+      <c r="N35" s="63"/>
       <c r="O35" s="8"/>
     </row>
     <row r="36" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -1628,11 +1629,11 @@
       <c r="J37" s="17" t="s">
         <v>43</v>
       </c>
-      <c r="L37" s="72" t="s">
+      <c r="L37" s="69" t="s">
         <v>27</v>
       </c>
-      <c r="M37" s="73"/>
-      <c r="N37" s="74"/>
+      <c r="M37" s="70"/>
+      <c r="N37" s="71"/>
       <c r="O37" s="8"/>
     </row>
     <row r="38" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -1772,12 +1773,12 @@
       <c r="F50" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="G50" s="70" t="str">
+      <c r="G50" s="64" t="str">
         <f>M30</f>
         <v>11-14-2025</v>
       </c>
-      <c r="H50" s="53"/>
-      <c r="I50" s="53"/>
+      <c r="H50" s="63"/>
+      <c r="I50" s="63"/>
       <c r="K50" s="45" t="s">
         <v>37</v>
       </c>
@@ -1806,11 +1807,16 @@
     <row r="52" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.3"/>
   </sheetData>
   <mergeCells count="38">
-    <mergeCell ref="A1:O1"/>
-    <mergeCell ref="D7:G7"/>
-    <mergeCell ref="J33:N33"/>
-    <mergeCell ref="E2:K2"/>
-    <mergeCell ref="M4:N4"/>
+    <mergeCell ref="J35:N35"/>
+    <mergeCell ref="M30:N30"/>
+    <mergeCell ref="L11:N11"/>
+    <mergeCell ref="C6:G6"/>
+    <mergeCell ref="C5:D5"/>
+    <mergeCell ref="E5:F5"/>
+    <mergeCell ref="B28:C29"/>
+    <mergeCell ref="M5:N5"/>
+    <mergeCell ref="A27:O27"/>
+    <mergeCell ref="L28:L29"/>
     <mergeCell ref="G50:I50"/>
     <mergeCell ref="J7:N7"/>
     <mergeCell ref="J32:N32"/>
@@ -1827,24 +1833,28 @@
     <mergeCell ref="M28:M29"/>
     <mergeCell ref="C31:D31"/>
     <mergeCell ref="G29:I29"/>
+    <mergeCell ref="A1:O1"/>
+    <mergeCell ref="D7:G7"/>
+    <mergeCell ref="J33:N33"/>
+    <mergeCell ref="E2:K2"/>
+    <mergeCell ref="M4:N4"/>
     <mergeCell ref="C9:G9"/>
     <mergeCell ref="E31:F31"/>
     <mergeCell ref="M31:N31"/>
-    <mergeCell ref="J35:N35"/>
-    <mergeCell ref="M30:N30"/>
-    <mergeCell ref="L11:N11"/>
-    <mergeCell ref="C6:G6"/>
-    <mergeCell ref="C5:D5"/>
-    <mergeCell ref="E5:F5"/>
-    <mergeCell ref="B28:C29"/>
     <mergeCell ref="M2:M3"/>
     <mergeCell ref="G3:I3"/>
-    <mergeCell ref="M5:N5"/>
     <mergeCell ref="N2:N3"/>
-    <mergeCell ref="A27:O27"/>
-    <mergeCell ref="L28:L29"/>
     <mergeCell ref="B2:C3"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3B97C4ED-DA6C-4205-ABF6-4054594FEF1B}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>